--- a/prot/調査結果/第2回調査結果（54名）.xlsx
+++ b/prot/調査結果/第2回調査結果（54名）.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kanaji Rinntarou\Desktop\Torapon\prot\調査結果\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0DBB66E-5FE3-4D35-B21F-60DDC983A486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55311BF0-27E8-40A0-AEE1-62870888E2EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7C8D910D-AE4E-4AD5-A898-7629F0EB9761}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{7C8D910D-AE4E-4AD5-A898-7629F0EB9761}"/>
   </bookViews>
   <sheets>
     <sheet name="データ" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="40">
   <si>
     <t>質問</t>
     <rPh sb="0" eb="2">
@@ -460,6 +460,41 @@
     </rPh>
     <rPh sb="30" eb="31">
       <t>カン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1. 栗林公園の観光をもっと良いものにするには
+何があれば良いと思いますか？（複数回答可）</t>
+    <rPh sb="3" eb="5">
+      <t>リツリン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>コウエン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カンコウ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ナニ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>オモ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>フクスウ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>カイトウ</t>
+    </rPh>
+    <rPh sb="43" eb="44">
+      <t>カ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -646,30 +681,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -680,17 +697,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
@@ -701,16 +712,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -719,11 +727,32 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -756,62 +785,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="ja-JP"/>
-              <a:t>調査時の国別回答割合</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="ja-JP"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
+    <c:autoTitleDeleted val="1"/>
     <c:plotArea>
       <c:layout/>
       <c:pieChart>
@@ -938,7 +912,7 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                    <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                       <a:solidFill>
                         <a:schemeClr val="accent1"/>
                       </a:solidFill>
@@ -968,8 +942,8 @@
               <c:idx val="1"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="-5.2674123122106405E-2"/>
-                  <c:y val="-3.696261864145646E-2"/>
+                  <c:x val="-5.7489282798201528E-2"/>
+                  <c:y val="7.3439170242649052E-2"/>
                 </c:manualLayout>
               </c:layout>
               <c:spPr>
@@ -986,7 +960,7 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                    <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                       <a:solidFill>
                         <a:schemeClr val="accent2"/>
                       </a:solidFill>
@@ -1016,8 +990,8 @@
               <c:idx val="2"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="-1.9406255887091776E-2"/>
-                  <c:y val="-9.2406546603641254E-3"/>
+                  <c:x val="-9.6449981999764553E-2"/>
+                  <c:y val="2.755986395957381E-2"/>
                 </c:manualLayout>
               </c:layout>
               <c:spPr>
@@ -1034,7 +1008,7 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                    <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                       <a:solidFill>
                         <a:schemeClr val="accent3"/>
                       </a:solidFill>
@@ -1082,7 +1056,7 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                    <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                       <a:solidFill>
                         <a:schemeClr val="accent4"/>
                       </a:solidFill>
@@ -1108,6 +1082,32 @@
                 </c:ext>
               </c:extLst>
             </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="accent1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:txPr>
             <c:dLblPos val="outEnd"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
@@ -1248,75 +1248,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="dk1">
-                    <a:lumMod val="75000"/>
-                    <a:lumOff val="25000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>Q1. </a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="ja-JP"/>
-              <a:t>栗林公園観光にある課題は？</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:layout>
-        <c:manualLayout>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="0.18685957116472834"/>
-          <c:y val="3.5282961323947593E-2"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1">
-                  <a:lumMod val="75000"/>
-                  <a:lumOff val="25000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="ja-JP"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
+    <c:autoTitleDeleted val="1"/>
     <c:plotArea>
       <c:layout/>
       <c:pieChart>
@@ -1342,6 +1274,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-DB1C-4F9E-8EDC-D71F3103245E}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -1361,6 +1298,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-DB1C-4F9E-8EDC-D71F3103245E}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -1380,6 +1322,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-DB1C-4F9E-8EDC-D71F3103245E}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
@@ -1399,6 +1346,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-DB1C-4F9E-8EDC-D71F3103245E}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="4"/>
@@ -1418,6 +1370,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-DB1C-4F9E-8EDC-D71F3103245E}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="5"/>
@@ -1437,6 +1394,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000B-DB1C-4F9E-8EDC-D71F3103245E}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="6"/>
@@ -1458,6 +1420,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000D-DB1C-4F9E-8EDC-D71F3103245E}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:spPr>
@@ -1493,7 +1460,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1100" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="lt1"/>
                     </a:solidFill>
@@ -1617,6 +1584,167 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
+      <c:legendEntry>
+        <c:idx val="0"/>
+        <c:txPr>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1050" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="1"/>
+        <c:txPr>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1050" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="2"/>
+        <c:txPr>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1050" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="3"/>
+        <c:txPr>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1050" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="4"/>
+        <c:txPr>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1050" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="5"/>
+        <c:txPr>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1050" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="6"/>
+        <c:txPr>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1050" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+      </c:legendEntry>
       <c:overlay val="0"/>
       <c:spPr>
         <a:solidFill>
@@ -1636,7 +1764,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="dk1">
                   <a:lumMod val="75000"/>
@@ -1774,7 +1902,17 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="7.606178550578005E-2"/>
+          <c:y val="0.22214202741689318"/>
+          <c:w val="0.51537441862537625"/>
+          <c:h val="0.77785797258310685"/>
+        </c:manualLayout>
+      </c:layout>
       <c:pieChart>
         <c:varyColors val="1"/>
         <c:ser>
@@ -1800,7 +1938,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-8EE6-48B6-9EA4-28F886BDA8CD}"/>
+                <c16:uniqueId val="{00000020-4C96-46CE-8B03-45262CBB0FDB}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1824,7 +1962,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-8EE6-48B6-9EA4-28F886BDA8CD}"/>
+                <c16:uniqueId val="{00000022-4C96-46CE-8B03-45262CBB0FDB}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1848,7 +1986,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000007-8EE6-48B6-9EA4-28F886BDA8CD}"/>
+                <c16:uniqueId val="{00000024-4C96-46CE-8B03-45262CBB0FDB}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1872,7 +2010,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000009-8EE6-48B6-9EA4-28F886BDA8CD}"/>
+                <c16:uniqueId val="{00000026-4C96-46CE-8B03-45262CBB0FDB}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1896,7 +2034,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000B-8EE6-48B6-9EA4-28F886BDA8CD}"/>
+                <c16:uniqueId val="{00000028-4C96-46CE-8B03-45262CBB0FDB}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1920,7 +2058,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000D-8EE6-48B6-9EA4-28F886BDA8CD}"/>
+                <c16:uniqueId val="{0000002A-4C96-46CE-8B03-45262CBB0FDB}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1946,7 +2084,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000F-8EE6-48B6-9EA4-28F886BDA8CD}"/>
+                <c16:uniqueId val="{0000002C-4C96-46CE-8B03-45262CBB0FDB}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1984,7 +2122,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1100" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="lt1"/>
                     </a:solidFill>
@@ -2023,9 +2161,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>グラフ!$B$12:$B$15</c:f>
+              <c:f>グラフ!$B$12:$B$16</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>5(満足している）</c:v>
                 </c:pt>
@@ -2037,6 +2175,9 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1(満足していない）</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2067,7 +2208,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000010-8EE6-48B6-9EA4-28F886BDA8CD}"/>
+              <c16:uniqueId val="{0000002D-4C96-46CE-8B03-45262CBB0FDB}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2093,14 +2234,129 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
+      <c:legendEntry>
+        <c:idx val="0"/>
+        <c:txPr>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1050" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="1"/>
+        <c:txPr>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1050" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="2"/>
+        <c:txPr>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1050" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="3"/>
+        <c:txPr>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1050" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="4"/>
+        <c:txPr>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1050" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+      </c:legendEntry>
       <c:layout>
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.72034922219274222"/>
-          <c:y val="0.37296783274359241"/>
-          <c:w val="0.20567321647747303"/>
-          <c:h val="0.31873674867516494"/>
+          <c:x val="0.67846979594567836"/>
+          <c:y val="0.4034225893922736"/>
+          <c:w val="0.26202193540382124"/>
+          <c:h val="0.33221217468019409"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
@@ -2122,7 +2378,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="dk1">
                   <a:lumMod val="75000"/>
@@ -2219,8 +2475,8 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.18373084407901474"/>
-          <c:y val="3.9422748453861158E-2"/>
+          <c:x val="0.18685957116472834"/>
+          <c:y val="3.5282961323947593E-2"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
@@ -2280,7 +2536,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-5403-48B0-BD62-1025EF71FACB}"/>
+                <c16:uniqueId val="{00000020-F922-43B6-A92E-3AB44E62AAF0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2304,7 +2560,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-5403-48B0-BD62-1025EF71FACB}"/>
+                <c16:uniqueId val="{00000022-F922-43B6-A92E-3AB44E62AAF0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2328,7 +2584,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000007-5403-48B0-BD62-1025EF71FACB}"/>
+                <c16:uniqueId val="{00000024-F922-43B6-A92E-3AB44E62AAF0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2352,7 +2608,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000009-5403-48B0-BD62-1025EF71FACB}"/>
+                <c16:uniqueId val="{00000026-F922-43B6-A92E-3AB44E62AAF0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2376,7 +2632,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000B-5403-48B0-BD62-1025EF71FACB}"/>
+                <c16:uniqueId val="{00000028-F922-43B6-A92E-3AB44E62AAF0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2400,7 +2656,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000D-5403-48B0-BD62-1025EF71FACB}"/>
+                <c16:uniqueId val="{0000002A-F922-43B6-A92E-3AB44E62AAF0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2426,7 +2682,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000F-5403-48B0-BD62-1025EF71FACB}"/>
+                <c16:uniqueId val="{0000002C-F922-43B6-A92E-3AB44E62AAF0}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2464,7 +2720,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1100" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="lt1"/>
                     </a:solidFill>
@@ -2550,7 +2806,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000010-5403-48B0-BD62-1025EF71FACB}"/>
+              <c16:uniqueId val="{0000002D-F922-43B6-A92E-3AB44E62AAF0}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2576,14 +2832,129 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
+      <c:legendEntry>
+        <c:idx val="0"/>
+        <c:txPr>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1050" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="1"/>
+        <c:txPr>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1050" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="2"/>
+        <c:txPr>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1050" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="3"/>
+        <c:txPr>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1050" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="4"/>
+        <c:txPr>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1050" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+      </c:legendEntry>
       <c:layout>
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.72034922219274222"/>
-          <c:y val="0.37296783274359241"/>
-          <c:w val="0.20567321647747303"/>
-          <c:h val="0.31873674867516494"/>
+          <c:x val="0.78343788620831056"/>
+          <c:y val="0.40402122236080684"/>
+          <c:w val="0.1545904889884005"/>
+          <c:h val="0.33015296477737882"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
@@ -2605,7 +2976,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="dk1">
                   <a:lumMod val="75000"/>
@@ -2668,74 +3039,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="dk1">
-                    <a:lumMod val="75000"/>
-                    <a:lumOff val="25000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US" altLang="ja-JP"/>
-              <a:t>Q4. </a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="ja-JP" altLang="en-US"/>
-              <a:t>プロトタイプに感じる価値は？</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:layout>
-        <c:manualLayout>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="0.18373084407901474"/>
-          <c:y val="3.9422748453861158E-2"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1">
-                  <a:lumMod val="75000"/>
-                  <a:lumOff val="25000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
+    <c:autoTitleDeleted val="1"/>
     <c:plotArea>
       <c:layout/>
       <c:pieChart>
@@ -2763,7 +3067,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-CC2E-4C09-B463-4DED773BB25E}"/>
+                <c16:uniqueId val="{00000020-A497-4799-8065-7AC7996B7CCB}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2787,7 +3091,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-CC2E-4C09-B463-4DED773BB25E}"/>
+                <c16:uniqueId val="{00000022-A497-4799-8065-7AC7996B7CCB}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2811,7 +3115,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000007-CC2E-4C09-B463-4DED773BB25E}"/>
+                <c16:uniqueId val="{00000024-A497-4799-8065-7AC7996B7CCB}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2835,7 +3139,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000009-CC2E-4C09-B463-4DED773BB25E}"/>
+                <c16:uniqueId val="{00000026-A497-4799-8065-7AC7996B7CCB}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2859,7 +3163,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000B-CC2E-4C09-B463-4DED773BB25E}"/>
+                <c16:uniqueId val="{00000028-A497-4799-8065-7AC7996B7CCB}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2883,7 +3187,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000D-CC2E-4C09-B463-4DED773BB25E}"/>
+                <c16:uniqueId val="{0000002A-A497-4799-8065-7AC7996B7CCB}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2909,7 +3213,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000F-CC2E-4C09-B463-4DED773BB25E}"/>
+                <c16:uniqueId val="{0000002C-A497-4799-8065-7AC7996B7CCB}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2947,7 +3251,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1100" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="lt1"/>
                     </a:solidFill>
@@ -3039,7 +3343,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000010-CC2E-4C09-B463-4DED773BB25E}"/>
+              <c16:uniqueId val="{0000002D-A497-4799-8065-7AC7996B7CCB}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3065,14 +3369,152 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
+      <c:legendEntry>
+        <c:idx val="0"/>
+        <c:txPr>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1050" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="1"/>
+        <c:txPr>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1050" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="2"/>
+        <c:txPr>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1050" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="3"/>
+        <c:txPr>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1050" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="4"/>
+        <c:txPr>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1050" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="5"/>
+        <c:txPr>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1050" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+      </c:legendEntry>
       <c:layout>
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.61777319004577158"/>
-          <c:y val="0.21990121026538351"/>
-          <c:w val="0.34172253729508834"/>
-          <c:h val="0.63860656346223865"/>
+          <c:x val="0.67846973705113489"/>
+          <c:y val="0.16029622751040709"/>
+          <c:w val="0.26202193540382124"/>
+          <c:h val="0.65752212795020237"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
@@ -3094,7 +3536,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="dk1">
                   <a:lumMod val="75000"/>
@@ -6307,16 +6749,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>52773</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>108857</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>534035</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>209120</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>661394</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>152666</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>480920</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>172718</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -6343,16 +6785,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>272824</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>473350</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>20052</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>30</xdr:col>
-      <xdr:colOff>252852</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>225690</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>453379</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>205637</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -6379,16 +6821,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>30</xdr:col>
-      <xdr:colOff>393508</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>164350</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>333350</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>124245</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>38</xdr:col>
-      <xdr:colOff>380496</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>225198</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>320339</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>64777</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -6415,16 +6857,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>30</xdr:col>
-      <xdr:colOff>531595</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>103655</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>651910</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>63549</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>38</xdr:col>
-      <xdr:colOff>594162</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>194931</xdr:rowOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>52741</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>114720</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -6787,7 +7229,7 @@
       <c r="G2" t="s">
         <v>33</v>
       </c>
-      <c r="H2" s="25">
+      <c r="H2" s="12">
         <v>45703</v>
       </c>
       <c r="I2" t="s">
@@ -6795,563 +7237,503 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A3" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="7" t="s">
+      <c r="A3" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="18"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="E3" s="7"/>
-      <c r="F3" s="9" t="s">
+      <c r="E3" s="18"/>
+      <c r="F3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="10" t="s">
+      <c r="I3" s="4" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="20"/>
-      <c r="I4" s="21"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="11"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A5" s="13"/>
-      <c r="B5" s="11" t="s">
+      <c r="A5" s="6"/>
+      <c r="B5" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11">
+      <c r="F5">
         <v>10</v>
       </c>
-      <c r="G5" s="11">
-        <v>0</v>
-      </c>
-      <c r="H5" s="11">
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
         <v>2</v>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="13"/>
-      <c r="B6" s="11" t="s">
+      <c r="A6" s="6"/>
+      <c r="B6" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11">
+      <c r="F6">
         <v>12</v>
       </c>
-      <c r="G6" s="11">
-        <v>0</v>
-      </c>
-      <c r="H6" s="11">
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
         <v>1</v>
       </c>
-      <c r="I6" s="12">
+      <c r="I6" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A7" s="13"/>
-      <c r="B7" s="11" t="s">
+      <c r="A7" s="6"/>
+      <c r="B7" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11">
+      <c r="F7">
         <v>5</v>
       </c>
-      <c r="G7" s="11">
-        <v>0</v>
-      </c>
-      <c r="H7" s="11">
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
         <v>1</v>
       </c>
-      <c r="I7" s="12">
+      <c r="I7" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A8" s="13"/>
-      <c r="B8" s="11" t="s">
+      <c r="A8" s="6"/>
+      <c r="B8" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11">
+      <c r="F8">
         <v>3</v>
       </c>
-      <c r="G8" s="11">
-        <v>0</v>
-      </c>
-      <c r="H8" s="11">
-        <v>0</v>
-      </c>
-      <c r="I8" s="12">
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A9" s="13"/>
-      <c r="B9" s="11" t="s">
+      <c r="A9" s="6"/>
+      <c r="B9" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11">
-        <v>0</v>
-      </c>
-      <c r="G9" s="11">
-        <v>0</v>
-      </c>
-      <c r="H9" s="11">
-        <v>0</v>
-      </c>
-      <c r="I9" s="12">
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A10" s="13"/>
-      <c r="B10" s="11" t="s">
+      <c r="A10" s="6"/>
+      <c r="B10" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11">
+      <c r="F10">
         <v>3</v>
       </c>
-      <c r="G10" s="11">
-        <v>0</v>
-      </c>
-      <c r="H10" s="11">
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
         <v>2</v>
       </c>
-      <c r="I10" s="12">
+      <c r="I10" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A11" s="15"/>
-      <c r="B11" s="16" t="s">
+      <c r="A11" s="7"/>
+      <c r="B11" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16">
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8">
         <v>6</v>
       </c>
-      <c r="G11" s="16">
-        <v>0</v>
-      </c>
-      <c r="H11" s="16">
-        <v>0</v>
-      </c>
-      <c r="I11" s="17">
+      <c r="G11" s="8">
+        <v>0</v>
+      </c>
+      <c r="H11" s="8">
+        <v>0</v>
+      </c>
+      <c r="I11" s="9">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="47.4" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="22" t="s">
+      <c r="A12" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="23"/>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="20"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="20"/>
-      <c r="I12" s="21"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="11"/>
       <c r="M12" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A13" s="13"/>
-      <c r="B13" s="11" t="s">
+      <c r="A13" s="6"/>
+      <c r="B13" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11">
-        <v>0</v>
-      </c>
-      <c r="G13" s="11">
-        <v>0</v>
-      </c>
-      <c r="H13" s="11">
-        <v>0</v>
-      </c>
-      <c r="I13" s="12">
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14">
+      <c r="A14" s="6"/>
+      <c r="B14" s="1">
         <v>2</v>
       </c>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11">
-        <v>0</v>
-      </c>
-      <c r="G14" s="11">
-        <v>0</v>
-      </c>
-      <c r="H14" s="11">
-        <v>0</v>
-      </c>
-      <c r="I14" s="12">
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14">
+      <c r="A15" s="6"/>
+      <c r="B15" s="1">
         <v>3</v>
       </c>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11">
+      <c r="F15">
         <v>9</v>
       </c>
-      <c r="G15" s="11">
-        <v>0</v>
-      </c>
-      <c r="H15" s="11">
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
         <v>3</v>
       </c>
-      <c r="I15" s="12">
+      <c r="I15" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14">
+      <c r="A16" s="6"/>
+      <c r="B16" s="1">
         <v>4</v>
       </c>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11">
+      <c r="F16">
         <v>6</v>
       </c>
-      <c r="G16" s="11">
-        <v>0</v>
-      </c>
-      <c r="H16" s="11">
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
         <v>1</v>
       </c>
-      <c r="I16" s="12">
+      <c r="I16" s="5">
         <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A17" s="15"/>
-      <c r="B17" s="16" t="s">
+      <c r="A17" s="7"/>
+      <c r="B17" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="16">
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8">
         <v>27</v>
       </c>
-      <c r="G17" s="16">
-        <v>0</v>
-      </c>
-      <c r="H17" s="16">
+      <c r="G17" s="8">
+        <v>0</v>
+      </c>
+      <c r="H17" s="8">
         <v>5</v>
       </c>
-      <c r="I17" s="17">
+      <c r="I17" s="9">
         <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="22" t="s">
+      <c r="A18" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B18" s="23"/>
-      <c r="C18" s="23"/>
-      <c r="D18" s="23"/>
-      <c r="E18" s="23"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="20"/>
-      <c r="H18" s="20"/>
-      <c r="I18" s="21"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="11"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A19" s="13"/>
-      <c r="B19" s="11" t="s">
+      <c r="A19" s="6"/>
+      <c r="B19" t="s">
         <v>12</v>
       </c>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11">
-        <v>0</v>
-      </c>
-      <c r="G19" s="11">
-        <v>0</v>
-      </c>
-      <c r="H19" s="11">
-        <v>0</v>
-      </c>
-      <c r="I19" s="12">
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A20" s="13"/>
-      <c r="B20" s="11" t="s">
+      <c r="A20" s="6"/>
+      <c r="B20" t="s">
         <v>13</v>
       </c>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11">
+      <c r="F20">
         <v>9</v>
       </c>
-      <c r="G20" s="11">
-        <v>0</v>
-      </c>
-      <c r="H20" s="11">
-        <v>0</v>
-      </c>
-      <c r="I20" s="12">
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A21" s="13"/>
-      <c r="B21" s="11" t="s">
+      <c r="A21" s="6"/>
+      <c r="B21" t="s">
         <v>14</v>
       </c>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11">
+      <c r="F21">
         <v>20</v>
       </c>
-      <c r="G21" s="11">
-        <v>0</v>
-      </c>
-      <c r="H21" s="11">
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
         <v>1</v>
       </c>
-      <c r="I21" s="12">
+      <c r="I21" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A22" s="13"/>
-      <c r="B22" s="11" t="s">
+      <c r="A22" s="6"/>
+      <c r="B22" t="s">
         <v>15</v>
       </c>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11">
+      <c r="F22">
         <v>6</v>
       </c>
-      <c r="G22" s="11">
-        <v>0</v>
-      </c>
-      <c r="H22" s="11">
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
         <v>1</v>
       </c>
-      <c r="I22" s="12">
+      <c r="I22" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A23" s="15"/>
-      <c r="B23" s="16" t="s">
+      <c r="A23" s="7"/>
+      <c r="B23" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C23" s="16"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="16">
-        <v>0</v>
-      </c>
-      <c r="G23" s="16">
-        <v>0</v>
-      </c>
-      <c r="H23" s="16">
-        <v>0</v>
-      </c>
-      <c r="I23" s="17">
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8">
+        <v>0</v>
+      </c>
+      <c r="G23" s="8">
+        <v>0</v>
+      </c>
+      <c r="H23" s="8">
+        <v>0</v>
+      </c>
+      <c r="I23" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="52.2" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A24" s="18" t="s">
+      <c r="A24" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="24"/>
-      <c r="C24" s="24"/>
-      <c r="D24" s="24"/>
-      <c r="E24" s="24"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="11"/>
-      <c r="H24" s="11"/>
-      <c r="I24" s="12"/>
+      <c r="B24" s="16"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
+      <c r="I24" s="5"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A25" s="13"/>
-      <c r="B25" s="11" t="s">
+      <c r="A25" s="6"/>
+      <c r="B25" t="s">
         <v>17</v>
       </c>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="11">
+      <c r="F25">
         <v>17</v>
       </c>
-      <c r="G25" s="11">
-        <v>0</v>
-      </c>
-      <c r="H25" s="11">
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
         <v>1</v>
       </c>
-      <c r="I25" s="12">
+      <c r="I25" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A26" s="13"/>
-      <c r="B26" s="11" t="s">
+      <c r="A26" s="6"/>
+      <c r="B26" t="s">
         <v>18</v>
       </c>
-      <c r="C26" s="11"/>
-      <c r="D26" s="11"/>
-      <c r="E26" s="11"/>
-      <c r="F26" s="11">
+      <c r="F26">
         <v>13</v>
       </c>
-      <c r="G26" s="11">
-        <v>0</v>
-      </c>
-      <c r="H26" s="11">
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
         <v>2</v>
       </c>
-      <c r="I26" s="12">
+      <c r="I26" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A27" s="13"/>
-      <c r="B27" s="11" t="s">
+      <c r="A27" s="6"/>
+      <c r="B27" t="s">
         <v>19</v>
       </c>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11">
+      <c r="F27">
         <v>5</v>
       </c>
-      <c r="G27" s="11">
-        <v>0</v>
-      </c>
-      <c r="H27" s="11">
-        <v>0</v>
-      </c>
-      <c r="I27" s="12">
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27" s="5">
         <v>4</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A28" s="13"/>
-      <c r="B28" s="11" t="s">
+      <c r="A28" s="6"/>
+      <c r="B28" t="s">
         <v>20</v>
       </c>
-      <c r="C28" s="11"/>
-      <c r="D28" s="11"/>
-      <c r="E28" s="11"/>
-      <c r="F28" s="11">
+      <c r="F28">
         <v>8</v>
       </c>
-      <c r="G28" s="11">
-        <v>0</v>
-      </c>
-      <c r="H28" s="11">
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
         <v>1</v>
       </c>
-      <c r="I28" s="12">
+      <c r="I28" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A29" s="13"/>
-      <c r="B29" s="11" t="s">
+      <c r="A29" s="6"/>
+      <c r="B29" t="s">
         <v>21</v>
       </c>
-      <c r="C29" s="11"/>
-      <c r="D29" s="11"/>
-      <c r="E29" s="11"/>
-      <c r="F29" s="11">
+      <c r="F29">
         <v>9</v>
       </c>
-      <c r="G29" s="11">
-        <v>0</v>
-      </c>
-      <c r="H29" s="11">
-        <v>0</v>
-      </c>
-      <c r="I29" s="12">
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A30" s="15"/>
-      <c r="B30" s="16" t="s">
+      <c r="A30" s="7"/>
+      <c r="B30" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C30" s="16"/>
-      <c r="D30" s="16"/>
-      <c r="E30" s="16"/>
-      <c r="F30" s="16">
-        <v>0</v>
-      </c>
-      <c r="G30" s="16">
-        <v>0</v>
-      </c>
-      <c r="H30" s="16">
-        <v>0</v>
-      </c>
-      <c r="I30" s="17">
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8">
+        <v>0</v>
+      </c>
+      <c r="G30" s="8">
+        <v>0</v>
+      </c>
+      <c r="H30" s="8">
+        <v>0</v>
+      </c>
+      <c r="I30" s="9">
         <v>0</v>
       </c>
     </row>
@@ -7374,6 +7756,7 @@
   <dimension ref="A1:M31"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
+    <col min="2" max="2" width="19.296875" customWidth="1"/>
     <col min="6" max="6" width="12.19921875" customWidth="1"/>
     <col min="7" max="7" width="10.3984375" customWidth="1"/>
     <col min="8" max="8" width="10.796875" customWidth="1"/>
@@ -7402,13 +7785,13 @@
       </c>
     </row>
     <row r="2" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
+      <c r="A2" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.45">
       <c r="B3" t="s">
@@ -7427,7 +7810,7 @@
         <v>2</v>
       </c>
       <c r="J3">
-        <f>SUM(F3:I3)</f>
+        <f t="shared" ref="J3:J9" si="0">SUM(F3:I3)</f>
         <v>15</v>
       </c>
       <c r="L3" t="s">
@@ -7454,7 +7837,7 @@
         <v>1</v>
       </c>
       <c r="J4">
-        <f>SUM(F4:I4)</f>
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="L4" t="s">
@@ -7481,7 +7864,7 @@
         <v>2</v>
       </c>
       <c r="J5">
-        <f>SUM(F5:I5)</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="L5" t="s">
@@ -7508,7 +7891,7 @@
         <v>1</v>
       </c>
       <c r="J6">
-        <f>SUM(F6:I6)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
@@ -7529,7 +7912,7 @@
         <v>1</v>
       </c>
       <c r="J7">
-        <f>SUM(F7:I7)</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
@@ -7550,7 +7933,7 @@
         <v>1</v>
       </c>
       <c r="J8">
-        <f>SUM(F8:I8)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
@@ -7571,18 +7954,18 @@
         <v>2</v>
       </c>
       <c r="J9">
-        <f>SUM(F9:I9)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="47.4" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
+      <c r="B11" s="23"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="23"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
@@ -7601,7 +7984,7 @@
         <v>2</v>
       </c>
       <c r="J12">
-        <f t="shared" ref="J4:J31" si="0">SUM(F12:I12)</f>
+        <f t="shared" ref="J12:J16" si="1">SUM(F12:I12)</f>
         <v>34</v>
       </c>
     </row>
@@ -7622,7 +8005,7 @@
         <v>6</v>
       </c>
       <c r="J13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
     </row>
@@ -7643,7 +8026,7 @@
         <v>0</v>
       </c>
       <c r="J14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
     </row>
@@ -7664,7 +8047,7 @@
         <v>0</v>
       </c>
       <c r="J15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -7685,18 +8068,18 @@
         <v>0</v>
       </c>
       <c r="J16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
+      <c r="B18" s="23"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="23"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B19" t="s">
@@ -7804,13 +8187,13 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="52.2" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
+      <c r="B25" s="21"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B26" t="s">
@@ -7829,7 +8212,7 @@
         <v>3</v>
       </c>
       <c r="J26">
-        <f>SUM(F26:I26)</f>
+        <f t="shared" ref="J26:J31" si="2">SUM(F26:I26)</f>
         <v>21</v>
       </c>
     </row>
@@ -7850,7 +8233,7 @@
         <v>3</v>
       </c>
       <c r="J27">
-        <f>SUM(F27:I27)</f>
+        <f t="shared" si="2"/>
         <v>18</v>
       </c>
     </row>
@@ -7871,7 +8254,7 @@
         <v>2</v>
       </c>
       <c r="J28">
-        <f>SUM(F28:I28)</f>
+        <f t="shared" si="2"/>
         <v>11</v>
       </c>
     </row>
@@ -7892,7 +8275,7 @@
         <v>1</v>
       </c>
       <c r="J29">
-        <f>SUM(F29:I29)</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
     </row>
@@ -7913,7 +8296,7 @@
         <v>4</v>
       </c>
       <c r="J30">
-        <f>SUM(F30:I30)</f>
+        <f t="shared" si="2"/>
         <v>9</v>
       </c>
     </row>
@@ -7934,7 +8317,7 @@
         <v>0</v>
       </c>
       <c r="J31">
-        <f>SUM(F31:I31)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>

--- a/prot/調査結果/第2回調査結果（54名）.xlsx
+++ b/prot/調査結果/第2回調査結果（54名）.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kanaji Rinntarou\Desktop\Torapon\prot\調査結果\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55311BF0-27E8-40A0-AEE1-62870888E2EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{207548CE-A644-45A2-BC57-2DF0BF6A26CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{7C8D910D-AE4E-4AD5-A898-7629F0EB9761}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="44">
   <si>
     <t>質問</t>
     <rPh sb="0" eb="2">
@@ -496,6 +496,31 @@
     <rPh sb="43" eb="44">
       <t>カ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>5（とても満足）</t>
+    <rPh sb="5" eb="7">
+      <t>マンゾク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3（ふつう）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>4（やや満足）</t>
+    <rPh sb="4" eb="6">
+      <t>マンゾク</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>マンゾク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2（あまり）</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1853,10 +1878,6 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>Q2. </a:t>
-            </a:r>
-            <a:r>
               <a:rPr lang="ja-JP" altLang="en-US"/>
               <a:t>栗林公園の観光の満足度は？</a:t>
             </a:r>
@@ -2165,16 +2186,16 @@
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>5(満足している）</c:v>
+                  <c:v>5（とても満足）</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4</c:v>
+                  <c:v>4（やや満足）</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3</c:v>
+                  <c:v>3（ふつう）</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2</c:v>
+                  <c:v>2（あまり）</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>1(満足していない）</c:v>
@@ -7969,7 +7990,7 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="F12">
         <v>27</v>
@@ -7989,8 +8010,8 @@
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="B13" s="1">
-        <v>4</v>
+      <c r="B13" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="F13">
         <v>6</v>
@@ -8010,8 +8031,8 @@
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="B14" s="1">
-        <v>3</v>
+      <c r="B14" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="F14">
         <v>9</v>
@@ -8031,8 +8052,8 @@
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="B15" s="1">
-        <v>2</v>
+      <c r="B15" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="F15">
         <v>0</v>
